--- a/data/merged/2026-09-09/MERGED_FR_Spot-Cleaner_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_FR_Spot-Cleaner_2026-09-09.xlsx
@@ -6255,13 +6255,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6299,13 +6299,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6695,13 +6695,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6739,13 +6739,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7130,50 +7130,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7499,7 +7455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -14452,40 +14408,40 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B07999DC2C</t>
+          <t>B0FD9R33PF</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>welsauber</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B07999DC2C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=welsauber</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Bissell Brosse pour Taches Tenaces, Noir, 15 cm</t>
+          <t>Welsauber Shampouineuse Canapé et Tapis 600W, Nettoyeur Textile 18 kPa avec Aspiration Puissante, Injecteur Extracteur pour C</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B07999DC2C?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FD9R33PF?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61aI3+gXJwL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/715cAyIFD7L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B07999DC2C</t>
+          <t>B0FD9R33PF</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -14499,113 +14455,117 @@
         </is>
       </c>
       <c r="O31" s="15">
-        <v>6571</v>
+        <v>9040</v>
       </c>
       <c r="P31" s="15">
-        <v>-2679</v>
+        <v>22287</v>
       </c>
       <c r="Q31" s="16">
-        <v>-0.69</v>
+        <v>0.72</v>
       </c>
       <c r="R31" s="17" t="inlineStr">
         <is>
-          <t>Nettoyeurs tapis et moquettes
-Accessoires pour nettoyeurs vapeur</t>
+          <t>Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>25
-30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T31" s="15">
-        <v>490</v>
+        <v>148</v>
       </c>
       <c r="U31" s="16">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="V31" s="15">
-        <v>12245</v>
+        <v>11247</v>
       </c>
       <c r="W31" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X31" s="15">
-        <v>2700</v>
+        <v>3884</v>
       </c>
       <c r="Y31" s="19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="20">
-        <v>20.82</v>
+        <v>75.99</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
-      <c r="AC31" s="2">
-        <v>4</v>
-      </c>
+      <c r="AC31" s="2"/>
       <c r="AD31" s="19">
-        <v>1382</v>
+        <v>363</v>
       </c>
       <c r="AE31" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF31" s="21">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG31" s="22">
-        <v>0.0204</v>
+        <v>0</v>
       </c>
       <c r="AH31" s="20">
-        <v>5.15</v>
+        <v>8.68</v>
       </c>
       <c r="AI31" s="16">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AJ31"/>
       <c r="AK31" s="13" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AL31" s="19">
-        <v>3022</v>
+        <v>383</v>
       </c>
       <c r="AM31" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN31" s="13"/>
       <c r="AO31" s="13"/>
       <c r="AP31"/>
       <c r="AQ31" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR31" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS31" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Welsauber Store</t>
         </is>
       </c>
       <c r="AT31" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU31" s="13"/>
-      <c r="AV31" s="14"/>
-      <c r="AW31" s="13"/>
-      <c r="AX31" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU31" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV31" s="14" t="inlineStr">
+        <is>
+          <t>深圳市 广东 518000 CN</t>
+        </is>
+      </c>
+      <c r="AW31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYFJ11UI07NEJ</t>
+        </is>
+      </c>
+      <c r="AX31" s="13"/>
       <c r="AY31" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14619,11 +14579,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD31" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD31" s="13"/>
       <c r="BE31" s="13"/>
       <c r="BF31" s="13"/>
       <c r="BG31" s="13"/>
@@ -14635,47 +14591,47 @@
       </c>
       <c r="BJ31" s="23" t="inlineStr">
         <is>
-          <t>137 g</t>
+          <t>3 kg</t>
         </is>
       </c>
       <c r="BK31" s="23" t="inlineStr">
         <is>
-          <t>137.00 g</t>
+          <t>3.00 kg</t>
         </is>
       </c>
       <c r="BL31" s="23" t="inlineStr">
         <is>
-          <t>40 x 25 x 15 cm</t>
+          <t>43 x 20 x 33 cm</t>
         </is>
       </c>
       <c r="BM31" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 25.00 x 15.00 cm</t>
+          <t>43.00 x 20.00 x 33.00 cm</t>
         </is>
       </c>
       <c r="BN31" s="23" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>4.19 kg</t>
         </is>
       </c>
       <c r="BO31" s="23" t="inlineStr">
         <is>
-          <t>150.00 g</t>
+          <t>4.19 kg</t>
         </is>
       </c>
       <c r="BP31" s="23" t="inlineStr">
         <is>
-          <t>16.5 x 15 x 7.3 cm</t>
+          <t>45.7 x 34.4 x 19.8 cm</t>
         </is>
       </c>
       <c r="BQ31" s="23" t="inlineStr">
         <is>
-          <t>16.50 x 15.00 x 7.30 cm</t>
+          <t>45.70 x 34.40 x 19.80 cm</t>
         </is>
       </c>
       <c r="BR31" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -14686,40 +14642,40 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0FD9R33PF</t>
+          <t>B0CLYF3DMZ</t>
         </is>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>welsauber</t>
+          <t>LEHMANN</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=welsauber</t>
+          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Welsauber Shampouineuse Canapé et Tapis 600W, Nettoyeur Textile 18 kPa avec Aspiration Puissante, Injecteur Extracteur pour C</t>
+          <t>Lehmann Prowash 2000 Professionnel Aspirateur Nettoyeur, Multifonction Shampouineuse Idéal pour Canapé, Tapis, Rembourrage, V</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FD9R33PF?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/715cAyIFD7L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0FD9R33PF</t>
+          <t>B0CLYF3DMZ</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -14733,13 +14689,13 @@
         </is>
       </c>
       <c r="O32" s="15">
-        <v>9040</v>
+        <v>38732</v>
       </c>
       <c r="P32" s="15">
-        <v>22287</v>
+        <v>-4625</v>
       </c>
       <c r="Q32" s="16">
-        <v>0.72</v>
+        <v>-0.22</v>
       </c>
       <c r="R32" s="17" t="inlineStr">
         <is>
@@ -14748,65 +14704,59 @@
       </c>
       <c r="S32" s="18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T32" s="15">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="U32" s="16">
-        <v>0.22</v>
+        <v>-0.7</v>
       </c>
       <c r="V32" s="15">
-        <v>11247</v>
-      </c>
-      <c r="W32" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X32" s="15">
-        <v>3884</v>
-      </c>
+        <v>11179</v>
+      </c>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
       <c r="Y32" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="20">
-        <v>75.99</v>
+        <v>129.99</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="19">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="AE32" s="15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AF32" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG32" s="22">
-        <v>0</v>
+        <v>0.1744</v>
       </c>
       <c r="AH32" s="20">
-        <v>8.68</v>
+        <v>9.96</v>
       </c>
       <c r="AI32" s="16">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="AJ32"/>
       <c r="AK32" s="13" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AL32" s="19">
-        <v>383</v>
+        <v>903</v>
       </c>
       <c r="AM32" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN32" s="13"/>
@@ -14820,27 +14770,27 @@
       </c>
       <c r="AS32" s="14" t="inlineStr">
         <is>
-          <t>Welsauber Store</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT32" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU32" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="AV32" s="14" t="inlineStr">
         <is>
-          <t>深圳市 广东 518000 CN</t>
+          <t>Greater Poland 63-100 PL</t>
         </is>
       </c>
       <c r="AW32" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYFJ11UI07NEJ</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
         </is>
       </c>
       <c r="AX32" s="13"/>
@@ -14869,42 +14819,38 @@
       </c>
       <c r="BJ32" s="23" t="inlineStr">
         <is>
-          <t>3 kg</t>
+          <t>6,2 Kilograms</t>
         </is>
       </c>
       <c r="BK32" s="23" t="inlineStr">
         <is>
-          <t>3.00 kg</t>
+          <t>6.20 kg</t>
         </is>
       </c>
       <c r="BL32" s="23" t="inlineStr">
         <is>
-          <t>43 x 20 x 33 cm</t>
-        </is>
-      </c>
-      <c r="BM32" s="23" t="inlineStr">
-        <is>
-          <t>43.00 x 20.00 x 33.00 cm</t>
-        </is>
-      </c>
+          <t>51,3P x 27,5l x 28,8H centimètres</t>
+        </is>
+      </c>
+      <c r="BM32" s="23"/>
       <c r="BN32" s="23" t="inlineStr">
         <is>
-          <t>4.19 kg</t>
+          <t>7.77 kg</t>
         </is>
       </c>
       <c r="BO32" s="23" t="inlineStr">
         <is>
-          <t>4.19 kg</t>
+          <t>7.77 kg</t>
         </is>
       </c>
       <c r="BP32" s="23" t="inlineStr">
         <is>
-          <t>45.7 x 34.4 x 19.8 cm</t>
+          <t>54.8 x 37.1 x 30.8 cm</t>
         </is>
       </c>
       <c r="BQ32" s="23" t="inlineStr">
         <is>
-          <t>45.70 x 34.40 x 19.80 cm</t>
+          <t>54.80 x 37.10 x 30.80 cm</t>
         </is>
       </c>
       <c r="BR32" s="13" t="inlineStr">
@@ -14920,40 +14866,40 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0GHQWRZLV</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN</t>
+          <t>SIMPLUS</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQWRZLV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Lehmann Prowash 2000 Professionnel Aspirateur Nettoyeur, Multifonction Shampouineuse Idéal pour Canapé, Tapis, Rembourrage, V</t>
+          <t>SIMPLUS Shampouineuse à Vapeur 110 °C pour Canapés et Tissus, Noirs22 kPa, 1800W, Injecteur Extracteur, avec Double Réservo</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GHQWRZLV?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71LN+xCoF4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0GHQWRZLV</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
@@ -14967,13 +14913,13 @@
         </is>
       </c>
       <c r="O33" s="15">
-        <v>38732</v>
+        <v>19042</v>
       </c>
       <c r="P33" s="15">
-        <v>-4625</v>
+        <v>23097</v>
       </c>
       <c r="Q33" s="16">
-        <v>-0.22</v>
+        <v>0.55</v>
       </c>
       <c r="R33" s="17" t="inlineStr">
         <is>
@@ -14982,59 +14928,65 @@
       </c>
       <c r="S33" s="18" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T33" s="15">
+        <v>78</v>
+      </c>
+      <c r="U33" s="16">
+        <v>2.58</v>
+      </c>
+      <c r="V33" s="15">
+        <v>10529</v>
+      </c>
+      <c r="W33" s="15" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T33" s="15">
-        <v>86</v>
-      </c>
-      <c r="U33" s="16">
-        <v>-0.7</v>
-      </c>
-      <c r="V33" s="15">
-        <v>11179</v>
-      </c>
-      <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
+      <c r="X33" s="15">
+        <v>6620</v>
+      </c>
       <c r="Y33" s="19">
         <v>1</v>
       </c>
       <c r="Z33" s="20">
-        <v>129.99</v>
+        <v>134.99</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="19">
-        <v>389</v>
+        <v>31</v>
       </c>
       <c r="AE33" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AF33" s="21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG33" s="22">
-        <v>0.1744</v>
+        <v>0.24359999999999998</v>
       </c>
       <c r="AH33" s="20">
-        <v>9.96</v>
+        <v>8.89</v>
       </c>
       <c r="AI33" s="16">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AJ33"/>
       <c r="AK33" s="13" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AL33" s="19">
-        <v>903</v>
+        <v>153</v>
       </c>
       <c r="AM33" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN33" s="13"/>
@@ -15048,35 +15000,31 @@
       </c>
       <c r="AS33" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>Simplus Official</t>
         </is>
       </c>
       <c r="AT33" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU33" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV33" s="14" t="inlineStr">
         <is>
-          <t>Greater Poland 63-100 PL</t>
+          <t>HK 999077 HK</t>
         </is>
       </c>
       <c r="AW33" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A</t>
         </is>
       </c>
       <c r="AX33" s="13"/>
-      <c r="AY33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY33" s="13"/>
       <c r="AZ33" s="13"/>
       <c r="BA33" s="13"/>
       <c r="BB33" s="13"/>
@@ -15085,50 +15033,54 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD33" s="13"/>
+      <c r="BD33" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE33" s="13"/>
       <c r="BF33" s="13"/>
       <c r="BG33" s="13"/>
       <c r="BH33" s="14"/>
-      <c r="BI33" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI33" s="23"/>
       <c r="BJ33" s="23" t="inlineStr">
         <is>
-          <t>6,2 Kilograms</t>
+          <t>4.6 kg</t>
         </is>
       </c>
       <c r="BK33" s="23" t="inlineStr">
         <is>
-          <t>6.20 kg</t>
+          <t>4.60 kg</t>
         </is>
       </c>
       <c r="BL33" s="23" t="inlineStr">
         <is>
-          <t>51,3P x 27,5l x 28,8H centimètres</t>
-        </is>
-      </c>
-      <c r="BM33" s="23"/>
+          <t>35 x 22 x 32 cm</t>
+        </is>
+      </c>
+      <c r="BM33" s="23" t="inlineStr">
+        <is>
+          <t>35.00 x 22.00 x 32.00 cm</t>
+        </is>
+      </c>
       <c r="BN33" s="23" t="inlineStr">
         <is>
-          <t>7.77 kg</t>
+          <t>5.65 kg</t>
         </is>
       </c>
       <c r="BO33" s="23" t="inlineStr">
         <is>
-          <t>7.77 kg</t>
+          <t>5.65 kg</t>
         </is>
       </c>
       <c r="BP33" s="23" t="inlineStr">
         <is>
-          <t>54.8 x 37.1 x 30.8 cm</t>
+          <t>37.1 x 36.2 x 28.3 cm</t>
         </is>
       </c>
       <c r="BQ33" s="23" t="inlineStr">
         <is>
-          <t>54.80 x 37.10 x 30.80 cm</t>
+          <t>37.10 x 36.20 x 28.30 cm</t>
         </is>
       </c>
       <c r="BR33" s="13" t="inlineStr">
@@ -15144,40 +15096,40 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GHQWRZLV</t>
+          <t>B0GFKK2WXT</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS</t>
+          <t>Vacmaster</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQWRZLV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Vacmaster/page/1389DFA9-3AE6-4105-88E0-C76D00DC1B2D?lp_asin=B0GFKK2WXT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS Shampouineuse à Vapeur 110 °C pour Canapés et Tissus, Noirs22 kPa, 1800W, Injecteur Extracteur, avec Double Réservo</t>
+          <t>Vacmaster Nettoyeur tapis chauffant 1150W 17KPA auto-nettoyage canapésauto-nettoyage Aspirateur Nettoyeur à Vapeur 50°C Net</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GHQWRZLV?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GFKK2WXT?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71LN+xCoF4L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/412kfxWeU6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0GHQWRZLV</t>
+          <t>B0GFKK2WXT</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -15191,13 +15143,13 @@
         </is>
       </c>
       <c r="O34" s="15">
-        <v>19042</v>
+        <v>16038</v>
       </c>
       <c r="P34" s="15">
-        <v>23097</v>
+        <v>19093</v>
       </c>
       <c r="Q34" s="16">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -15206,31 +15158,25 @@
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T34" s="15">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="U34" s="16">
-        <v>2.58</v>
+        <v>-0.06</v>
       </c>
       <c r="V34" s="15">
-        <v>10529</v>
-      </c>
-      <c r="W34" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X34" s="15">
-        <v>6620</v>
-      </c>
+        <v>10079</v>
+      </c>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
       <c r="Y34" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z34" s="20">
-        <v>134.99</v>
+        <v>82.37</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
@@ -15239,32 +15185,32 @@
         <v>31</v>
       </c>
       <c r="AE34" s="15">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AF34" s="21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG34" s="22">
-        <v>0.24359999999999998</v>
+        <v>0.13390000000000002</v>
       </c>
       <c r="AH34" s="20">
-        <v>8.89</v>
+        <v>8.68</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN34" s="13"/>
@@ -15274,35 +15220,31 @@
         <v>10</v>
       </c>
       <c r="AR34" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Simplus Official</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU34" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV34" s="14" t="inlineStr">
-        <is>
-          <t>HK 999077 HK</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU34" s="13"/>
+      <c r="AV34" s="14"/>
       <c r="AW34" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUAKXO7WRPF4V</t>
         </is>
       </c>
       <c r="AX34" s="13"/>
-      <c r="AY34" s="13"/>
+      <c r="AY34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ34" s="13"/>
       <c r="BA34" s="13"/>
       <c r="BB34" s="13"/>
@@ -15320,45 +15262,49 @@
       <c r="BF34" s="13"/>
       <c r="BG34" s="13"/>
       <c r="BH34" s="14"/>
-      <c r="BI34" s="23"/>
+      <c r="BI34" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>4.6 kg</t>
+          <t>4,63 Kilograms</t>
         </is>
       </c>
       <c r="BK34" s="23" t="inlineStr">
         <is>
-          <t>4.60 kg</t>
+          <t>4.63 kg</t>
         </is>
       </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>35 x 22 x 32 cm</t>
+          <t>37,4 x 34,4 x 23,8 cm</t>
         </is>
       </c>
       <c r="BM34" s="23" t="inlineStr">
         <is>
-          <t>35.00 x 22.00 x 32.00 cm</t>
+          <t>37.40 x 34.40 x 23.80 cm</t>
         </is>
       </c>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>5.65 kg</t>
+          <t>4.63 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>5.65 kg</t>
+          <t>4.63 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>37.1 x 36.2 x 28.3 cm</t>
+          <t>37.7 x 34.9 x 23.9 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>37.10 x 36.20 x 28.30 cm</t>
+          <t>37.70 x 34.90 x 23.90 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
@@ -15374,121 +15320,125 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GFKK2WXT</t>
+          <t>B0C3VKT151</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster</t>
+          <t>SUPER CLEAN</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Vacmaster/page/1389DFA9-3AE6-4105-88E0-C76D00DC1B2D?lp_asin=B0GFKK2WXT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Nettoyeur tapis chauffant 1150W 17KPA auto-nettoyage canapésauto-nettoyage Aspirateur Nettoyeur à Vapeur 50°C Net</t>
+          <t>SUPER CLEAN Nettoyant concentré tapis et tissus nettoyage en profondeur adapté aux tapis sièges auto canapés contenu 2 x 500</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GFKK2WXT?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0C3VKT151?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/412kfxWeU6L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41xcF1ROXCL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GFKK2WXT</t>
+          <t>B0C3VKT151</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
+          <t>Cuisine et Maison:Produits et accessoires de nettoyage:Produits d'entretien:Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
+          <t>Voir les 100 premiers en Epicerie</t>
         </is>
       </c>
       <c r="O35" s="15">
-        <v>16038</v>
+        <v>1230</v>
       </c>
       <c r="P35" s="15">
-        <v>19093</v>
+        <v>-19</v>
       </c>
       <c r="Q35" s="16">
-        <v>0.65</v>
+        <v>-0.02</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
-          <t>Nettoyeurs tapis et moquettes</t>
+          <t>Nettoyants pour tapis de maison
+Produits d’entretien ménagers</t>
         </is>
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4
+193</t>
         </is>
       </c>
       <c r="T35" s="15">
-        <v>112</v>
+        <v>347</v>
       </c>
       <c r="U35" s="16">
-        <v>-0.06</v>
+        <v>0.19</v>
       </c>
       <c r="V35" s="15">
-        <v>10079</v>
+        <v>9938</v>
       </c>
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z35" s="20">
-        <v>82.37</v>
+        <v>28.64</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
-      <c r="AC35" s="2"/>
+      <c r="AC35" s="2">
+        <v>26</v>
+      </c>
       <c r="AD35" s="19">
-        <v>31</v>
+        <v>476</v>
       </c>
       <c r="AE35" s="15">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="AF35" s="21">
         <v>4.4</v>
       </c>
       <c r="AG35" s="22">
-        <v>0.13390000000000002</v>
+        <v>0.22190000000000001</v>
       </c>
       <c r="AH35" s="20">
-        <v>8.68</v>
+        <v>5.96</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>242</v>
+        <v>1154</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN35" s="13"/>
@@ -15498,31 +15448,35 @@
         <v>10</v>
       </c>
       <c r="AR35" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Innochem</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU35" s="13"/>
-      <c r="AV35" s="14"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU35" s="13" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AV35" s="14" t="inlineStr">
+        <is>
+          <t>Teningen 79331 DE</t>
+        </is>
+      </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUAKXO7WRPF4V</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
-      <c r="AY35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY35" s="13"/>
       <c r="AZ35" s="13"/>
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
@@ -15540,54 +15494,50 @@
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
       <c r="BH35" s="14"/>
-      <c r="BI35" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI35" s="23"/>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>4,63 Kilograms</t>
+          <t>250 grammes</t>
         </is>
       </c>
       <c r="BK35" s="23" t="inlineStr">
         <is>
-          <t>4.63 kg</t>
+          <t>250.00 g</t>
         </is>
       </c>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>37,4 x 34,4 x 23,8 cm</t>
+          <t>19,5 x 18,1 x 7,3 cm</t>
         </is>
       </c>
       <c r="BM35" s="23" t="inlineStr">
         <is>
-          <t>37.40 x 34.40 x 23.80 cm</t>
+          <t>19.50 x 18.10 x 7.30 cm</t>
         </is>
       </c>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>4.63 kg</t>
+          <t>1.11 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>4.63 kg</t>
+          <t>1.11 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>37.7 x 34.9 x 23.9 cm</t>
+          <t>19.5 x 18.1 x 7.3 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>37.70 x 34.90 x 23.90 cm</t>
+          <t>19.50 x 18.10 x 7.30 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -15598,121 +15548,123 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0C3VKT151</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>SUPER CLEAN</t>
+          <t>Livatro</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN</t>
+          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>SUPER CLEAN Nettoyant concentré tapis et tissus nettoyage en profondeur adapté aux tapis sièges auto canapés contenu 2 x 500</t>
+          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et TapissEau propre 2,3 L, eau sale 1,3 L pour nettoyer plus</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0C3VKT151?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41xcF1ROXCL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71nARwekliL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0C3VKT151</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Produits et accessoires de nettoyage:Produits d'entretien:Nettoyeurs tapis et moquettes</t>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="N36" s="14" t="inlineStr">
         <is>
-          <t>Voir les 100 premiers en Epicerie</t>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
         </is>
       </c>
       <c r="O36" s="15">
-        <v>1230</v>
+        <v>30859</v>
       </c>
       <c r="P36" s="15">
-        <v>-19</v>
+        <v>-11588</v>
       </c>
       <c r="Q36" s="16">
-        <v>-0.02</v>
+        <v>-0.6</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
-          <t>Nettoyants pour tapis de maison
-Produits d’entretien ménagers</t>
+          <t>Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>4
-193</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T36" s="15">
-        <v>347</v>
+        <v>124</v>
       </c>
       <c r="U36" s="16">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="V36" s="15">
-        <v>9938</v>
-      </c>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
+        <v>9422</v>
+      </c>
+      <c r="W36" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X36" s="15">
+        <v>3909</v>
+      </c>
       <c r="Y36" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z36" s="20">
-        <v>28.64</v>
+        <v>75.98</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
-      <c r="AC36" s="2">
-        <v>26</v>
-      </c>
+      <c r="AC36" s="2"/>
       <c r="AD36" s="19">
-        <v>476</v>
+        <v>336</v>
       </c>
       <c r="AE36" s="15">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="AF36" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG36" s="22">
-        <v>0.22190000000000001</v>
+        <v>0.2339</v>
       </c>
       <c r="AH36" s="20">
-        <v>5.96</v>
+        <v>8.68</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>1154</v>
+        <v>379</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
@@ -15726,11 +15678,11 @@
         <v>10</v>
       </c>
       <c r="AR36" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>Innochem</t>
+          <t>Kayon International</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
@@ -15740,21 +15692,25 @@
       </c>
       <c r="AU36" s="13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV36" s="14" t="inlineStr">
         <is>
-          <t>Teningen 79331 DE</t>
+          <t>HONGKONG 999077 HK</t>
         </is>
       </c>
       <c r="AW36" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B</t>
         </is>
       </c>
       <c r="AX36" s="13"/>
-      <c r="AY36" s="13"/>
+      <c r="AY36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ36" s="13"/>
       <c r="BA36" s="13"/>
       <c r="BB36" s="13"/>
@@ -15772,50 +15728,54 @@
       <c r="BF36" s="13"/>
       <c r="BG36" s="13"/>
       <c r="BH36" s="14"/>
-      <c r="BI36" s="23"/>
+      <c r="BI36" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>250 grammes</t>
+          <t>3.8 kg</t>
         </is>
       </c>
       <c r="BK36" s="23" t="inlineStr">
         <is>
-          <t>250.00 g</t>
+          <t>3.80 kg</t>
         </is>
       </c>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>19,5 x 18,1 x 7,3 cm</t>
+          <t>22.9 x 37 x 35.6 cm</t>
         </is>
       </c>
       <c r="BM36" s="23" t="inlineStr">
         <is>
-          <t>19.50 x 18.10 x 7.30 cm</t>
+          <t>22.90 x 37.00 x 35.60 cm</t>
         </is>
       </c>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>1.11 kg</t>
+          <t>4.66 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>1.11 kg</t>
+          <t>4.66 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>19.5 x 18.1 x 7.3 cm</t>
+          <t>45.1 x 36.6 x 20.5 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>19.50 x 18.10 x 7.30 cm</t>
+          <t>45.10 x 36.60 x 20.50 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -15826,40 +15786,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0GHQBM3W1</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Livatro</t>
+          <t>SIMPLUS</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQBM3W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et TapissEau propre 2,3 L, eau sale 1,3 L pour nettoyer plus</t>
+          <t>SIMPLUS Shampouineuse Canapé avec Fonction Autonettoyante, Nettoyeur Tissus Puissant 12000Pa, Idéal pour Poils d’Animaux, Net</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GHQBM3W1?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71nARwekliL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41d4NPDnU9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0GHQBM3W1</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -15873,13 +15833,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>30859</v>
+        <v>17291</v>
       </c>
       <c r="P37" s="15">
-        <v>-11588</v>
+        <v>-3130</v>
       </c>
       <c r="Q37" s="16">
-        <v>-0.6</v>
+        <v>-0.22</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -15888,17 +15848,17 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="U37" s="16">
-        <v>0.08</v>
+        <v>0.97</v>
       </c>
       <c r="V37" s="15">
-        <v>9422</v>
+        <v>7979</v>
       </c>
       <c r="W37" s="15" t="inlineStr">
         <is>
@@ -15906,43 +15866,43 @@
         </is>
       </c>
       <c r="X37" s="15">
-        <v>3909</v>
+        <v>3438</v>
       </c>
       <c r="Y37" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>75.98</v>
+        <v>69.99</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="19">
-        <v>336</v>
+        <v>47</v>
       </c>
       <c r="AE37" s="15">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AF37" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG37" s="22">
-        <v>0.2339</v>
+        <v>0.0702</v>
       </c>
       <c r="AH37" s="20">
-        <v>8.68</v>
+        <v>8.11</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>379</v>
+        <v>147</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
@@ -15956,11 +15916,11 @@
         <v>10</v>
       </c>
       <c r="AR37" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>Kayon International</t>
+          <t>Simplus Official</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
@@ -15975,12 +15935,12 @@
       </c>
       <c r="AV37" s="14" t="inlineStr">
         <is>
-          <t>HONGKONG 999077 HK</t>
+          <t>HK 999077 HK</t>
         </is>
       </c>
       <c r="AW37" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A</t>
         </is>
       </c>
       <c r="AX37" s="13"/>
@@ -16013,47 +15973,43 @@
       </c>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>3.8 kg</t>
+          <t>2,5 Kilograms</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>3.80 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>22.9 x 37 x 35.6 cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="23" t="inlineStr">
-        <is>
-          <t>22.90 x 37.00 x 35.60 cm</t>
-        </is>
-      </c>
+          <t>32,5P x 19l x 34,5H centimètres</t>
+        </is>
+      </c>
+      <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>4.66 kg</t>
+          <t>3.29 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>4.66 kg</t>
+          <t>3.29 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>45.1 x 36.6 x 20.5 cm</t>
+          <t>35.1 x 33.9 x 19.5 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>45.10 x 36.60 x 20.50 cm</t>
+          <t>35.10 x 33.90 x 19.50 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16064,40 +16020,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0GHQBM3W1</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQBM3W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS Shampouineuse Canapé avec Fonction Autonettoyante, Nettoyeur Tissus Puissant 12000Pa, Idéal pour Poils d’Animaux, Net</t>
+          <t>HAUSHOF StainZapper Shampouineuse 400 W avec Double RéservoirsNettoyeur de Tapis, Réservoirs 1,1 L + 0,5 L, Tuyau 1,2 m, 2</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GHQBM3W1?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41d4NPDnU9L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41mvaF7mrKL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0GHQBM3W1</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -16111,13 +16067,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>17291</v>
+        <v>27784</v>
       </c>
       <c r="P38" s="15">
-        <v>-3130</v>
+        <v>-13319</v>
       </c>
       <c r="Q38" s="16">
-        <v>-0.22</v>
+        <v>-0.48</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -16126,17 +16082,17 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>39</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="U38" s="16">
-        <v>0.97</v>
+        <v>-0.08</v>
       </c>
       <c r="V38" s="15">
-        <v>7979</v>
+        <v>7759</v>
       </c>
       <c r="W38" s="15" t="inlineStr">
         <is>
@@ -16144,47 +16100,47 @@
         </is>
       </c>
       <c r="X38" s="15">
-        <v>3438</v>
+        <v>3841</v>
       </c>
       <c r="Y38" s="19">
         <v>1</v>
       </c>
       <c r="Z38" s="20">
-        <v>69.99</v>
+        <v>79.99</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="19">
-        <v>47</v>
+        <v>4821</v>
       </c>
       <c r="AE38" s="15">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="AF38" s="21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG38" s="22">
-        <v>0.0702</v>
+        <v>0.3608</v>
       </c>
       <c r="AH38" s="20">
-        <v>8.11</v>
+        <v>8.47</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>147</v>
+        <v>1239</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN38" s="13"/>
@@ -16194,33 +16150,21 @@
         <v>10</v>
       </c>
       <c r="AR38" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
-          <t>Simplus Official</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT38" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU38" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV38" s="14" t="inlineStr">
-        <is>
-          <t>HK 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW38" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU38" s="13"/>
+      <c r="AV38" s="14"/>
+      <c r="AW38" s="13"/>
       <c r="AX38" s="13"/>
       <c r="AY38" s="13" t="inlineStr">
         <is>
@@ -16251,43 +16195,43 @@
       </c>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>2,5 Kilograms</t>
+          <t>3,4 Kilograms</t>
         </is>
       </c>
       <c r="BK38" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>3.40 kg</t>
         </is>
       </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>32,5P x 19l x 34,5H centimètres</t>
+          <t>15P x 28,5l x 26,5H centimètres</t>
         </is>
       </c>
       <c r="BM38" s="23"/>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>35.1 x 33.9 x 19.5 cm</t>
+          <t>40.2 x 34.2 x 19.5 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>35.10 x 33.90 x 19.50 cm</t>
+          <t>40.20 x 34.20 x 19.50 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16298,40 +16242,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0GZVZYBP4</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>SIMPLUS</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GZVZYBP4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Shampouineuse 400 W avec Double RéservoirsNettoyeur de Tapis, Réservoirs 1,1 L + 0,5 L, Tuyau 1,2 m, 2</t>
+          <t>SIMPLUS Shampouineuse à Vapeur 100 °C pour Canapés et Tissus, Blancs18 kPa, 1650W, Injecteur Extracteur Portable, avec Doub</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GZVZYBP4?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41mvaF7mrKL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41IR-fMqT2L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0GZVZYBP4</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -16345,13 +16289,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>27784</v>
+        <v>23906</v>
       </c>
       <c r="P39" s="15">
-        <v>-13319</v>
+        <v>48177</v>
       </c>
       <c r="Q39" s="16">
-        <v>-0.48</v>
+        <v>0.89</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16360,95 +16304,95 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>97</v>
-      </c>
-      <c r="U39" s="16">
-        <v>-0.08</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="U39" s="16"/>
       <c r="V39" s="15">
-        <v>7759</v>
-      </c>
-      <c r="W39" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X39" s="15">
-        <v>3841</v>
-      </c>
+        <v>7680</v>
+      </c>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
       <c r="Y39" s="19">
         <v>1</v>
       </c>
       <c r="Z39" s="20">
-        <v>79.99</v>
+        <v>99.74</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="19">
-        <v>4821</v>
+        <v>19</v>
       </c>
       <c r="AE39" s="15">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="AF39" s="21">
         <v>4.2</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.3608</v>
+        <v>0.2078</v>
       </c>
       <c r="AH39" s="20">
-        <v>8.47</v>
+        <v>8.68</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>1239</v>
+        <v>115</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN39" s="13"/>
       <c r="AO39" s="13"/>
       <c r="AP39"/>
       <c r="AQ39" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR39" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Simplus Official</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU39" s="13"/>
-      <c r="AV39" s="14"/>
-      <c r="AW39" s="13"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU39" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV39" s="14" t="inlineStr">
+        <is>
+          <t>HK 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW39" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A</t>
+        </is>
+      </c>
       <c r="AX39" s="13"/>
-      <c r="AY39" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY39" s="13"/>
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
@@ -16466,45 +16410,41 @@
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
       <c r="BH39" s="14"/>
-      <c r="BI39" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI39" s="23"/>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>3,4 Kilograms</t>
+          <t>4,92 Kilograms</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>3.40 kg</t>
+          <t>4.92 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>15P x 28,5l x 26,5H centimètres</t>
+          <t>33P x 22l x 33H centimètres</t>
         </is>
       </c>
       <c r="BM39" s="23"/>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>5.16 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>5.16 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>40.2 x 34.2 x 19.5 cm</t>
+          <t>37.6 x 37.4 x 24 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>40.20 x 34.20 x 19.50 cm</t>
+          <t>37.60 x 37.40 x 24.00 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
@@ -16520,40 +16460,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0GZVZYBP4</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS</t>
+          <t>H.Koenig</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GZVZYBP4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>SIMPLUS Shampouineuse à Vapeur 100 °C pour Canapés et Tissus, Blancs18 kPa, 1650W, Injecteur Extracteur Portable, avec Doub</t>
+          <t>H.Koenig Nettoyeur Détacheur TWT77, Shampouineuse, Nettoyeur Tapis Canapé et Tissu, Double Réservoir, Brosse de Rechange Incl</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GZVZYBP4?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41IR-fMqT2L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41EDgJP8-JL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0GZVZYBP4</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -16567,13 +16507,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>23906</v>
+        <v>35891</v>
       </c>
       <c r="P40" s="15">
-        <v>48177</v>
+        <v>-2041</v>
       </c>
       <c r="Q40" s="16">
-        <v>0.89</v>
+        <v>-0.09</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -16582,95 +16522,107 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>77</v>
-      </c>
-      <c r="U40" s="16"/>
+        <v>107</v>
+      </c>
+      <c r="U40" s="16">
+        <v>1.89</v>
+      </c>
       <c r="V40" s="15">
-        <v>7680</v>
-      </c>
-      <c r="W40" s="15"/>
-      <c r="X40" s="15"/>
+        <v>7479</v>
+      </c>
+      <c r="W40" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X40" s="15">
+        <v>3057</v>
+      </c>
       <c r="Y40" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z40" s="20">
-        <v>99.74</v>
+        <v>69.9</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="19">
-        <v>19</v>
+        <v>1077</v>
       </c>
       <c r="AE40" s="15">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AF40" s="21">
         <v>4.2</v>
       </c>
       <c r="AG40" s="22">
-        <v>0.2078</v>
+        <v>0.0467</v>
       </c>
       <c r="AH40" s="20">
-        <v>8.68</v>
+        <v>9.53</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>115</v>
+        <v>1298</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN40" s="13"/>
       <c r="AO40" s="13"/>
       <c r="AP40"/>
       <c r="AQ40" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR40" s="19">
         <v>1</v>
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>Simplus Official</t>
+          <t>HomeHome by A</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU40" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="AV40" s="14" t="inlineStr">
         <is>
-          <t>HK 999077 HK</t>
+          <t>Paris 75001 FR</t>
         </is>
       </c>
       <c r="AW40" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
         </is>
       </c>
       <c r="AX40" s="13"/>
-      <c r="AY40" s="13"/>
+      <c r="AY40" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ40" s="13"/>
       <c r="BA40" s="13"/>
       <c r="BB40" s="13"/>
@@ -16688,41 +16640,45 @@
       <c r="BF40" s="13"/>
       <c r="BG40" s="13"/>
       <c r="BH40" s="14"/>
-      <c r="BI40" s="23"/>
+      <c r="BI40" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>4,92 Kilograms</t>
+          <t>4 Kilograms</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>4.92 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>33P x 22l x 33H centimètres</t>
+          <t>36,5P x 24,5l x 31,8H centimètres</t>
         </is>
       </c>
       <c r="BM40" s="23"/>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>5.16 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>5.16 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>37.6 x 37.4 x 24 cm</t>
+          <t>45 x 38 x 29 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>37.60 x 37.40 x 24.00 cm</t>
+          <t>45.00 x 38.00 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
@@ -16738,40 +16694,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0H2VRP6P5</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig</t>
+          <t>STARRYBOT</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=STARRYBOT</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig Nettoyeur Détacheur TWT77, Shampouineuse, Nettoyeur Tapis Canapé et Tissu, Double Réservoir, Brosse de Rechange Incl</t>
+          <t>STARRYBOT Nettoyeur Vapeur Canapé Portable 18kPa, Shampouineuse GrissChauffage intégré pour taches d’animaux, tapis, escali</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H2VRP6P5?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41EDgJP8-JL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71gQgb5LadL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0H2VRP6P5</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16785,13 +16741,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>35891</v>
+        <v>5879</v>
       </c>
       <c r="P41" s="15">
-        <v>-2041</v>
+        <v>30177</v>
       </c>
       <c r="Q41" s="16">
-        <v>-0.09</v>
+        <v>0.85</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16800,61 +16756,53 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>107</v>
-      </c>
-      <c r="U41" s="16">
-        <v>1.89</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="U41" s="16"/>
       <c r="V41" s="15">
-        <v>7479</v>
-      </c>
-      <c r="W41" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X41" s="15">
-        <v>3057</v>
-      </c>
+        <v>7019</v>
+      </c>
+      <c r="W41" s="15"/>
+      <c r="X41" s="15"/>
       <c r="Y41" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z41" s="20">
-        <v>69.9</v>
+        <v>129.99</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="19">
-        <v>1077</v>
+        <v>22</v>
       </c>
       <c r="AE41" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="21">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.0467</v>
+        <v>0</v>
       </c>
       <c r="AH41" s="20">
-        <v>9.53</v>
+        <v>8.34</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>1298</v>
+        <v>93</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
@@ -16872,7 +16820,7 @@
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>HomeHome by A</t>
+          <t>HEYWORK</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
@@ -16882,17 +16830,17 @@
       </c>
       <c r="AU41" s="13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV41" s="14" t="inlineStr">
         <is>
-          <t>Paris 75001 FR</t>
+          <t>宁波市 浙江 315000 CN</t>
         </is>
       </c>
       <c r="AW41" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ</t>
         </is>
       </c>
       <c r="AX41" s="13"/>
@@ -16925,43 +16873,47 @@
       </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>4 Kilograms</t>
+          <t>5 kg</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>5.00 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>36,5P x 24,5l x 31,8H centimètres</t>
-        </is>
-      </c>
-      <c r="BM41" s="23"/>
+          <t>43 x 19.5 x 34 cm</t>
+        </is>
+      </c>
+      <c r="BM41" s="23" t="inlineStr">
+        <is>
+          <t>43.00 x 19.50 x 34.00 cm</t>
+        </is>
+      </c>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>5.1 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>5.10 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>45 x 38 x 29 cm</t>
+          <t>43 x 34 x 19.5 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>45.00 x 38.00 x 29.00 cm</t>
+          <t>43.00 x 34.00 x 19.50 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16972,40 +16924,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0H2VRP6P5</t>
+          <t>B0GDCZ7BWK</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>STARRYBOT</t>
+          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=STARRYBOT</t>
+          <t>https://www.amazon.fr/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/EFD3CB9F-9686-4148-8B39-B39106076EB5?lp_asin=B0GDCZ7BWK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>STARRYBOT Nettoyeur Vapeur Canapé Portable 18kPa, Shampouineuse GrissChauffage intégré pour taches d’animaux, tapis, escali</t>
+          <t>HYCHIKA Shampouineuse Canapé,Nettoyeur Canapé Tissu 1800Ws17 kPa Injecteur Extracteur Portable,avec Double Réservoir et Aut</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H2VRP6P5?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GDCZ7BWK?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71gQgb5LadL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51aWYbD9oWL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0H2VRP6P5</t>
+          <t>B0GDCZ7BWK</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -17019,13 +16971,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>5879</v>
+        <v>31125</v>
       </c>
       <c r="P42" s="15">
-        <v>30177</v>
+        <v>6591</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.85</v>
+        <v>0.15</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -17034,99 +16986,85 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>54</v>
-      </c>
-      <c r="U42" s="16"/>
+        <v>62</v>
+      </c>
+      <c r="U42" s="16">
+        <v>0.12</v>
+      </c>
       <c r="V42" s="15">
-        <v>7019</v>
+        <v>6744</v>
       </c>
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
       <c r="Y42" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>129.99</v>
+        <v>90.64</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="19">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="AE42" s="15">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF42" s="21">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AG42" s="22">
-        <v>0</v>
+        <v>0.5806</v>
       </c>
       <c r="AH42" s="20">
-        <v>8.34</v>
+        <v>8.68</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
       <c r="AO42" s="13"/>
       <c r="AP42"/>
       <c r="AQ42" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR42" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>HEYWORK</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU42" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV42" s="14" t="inlineStr">
-        <is>
-          <t>宁波市 浙江 315000 CN</t>
-        </is>
-      </c>
-      <c r="AW42" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU42" s="13"/>
+      <c r="AV42" s="14"/>
+      <c r="AW42" s="13"/>
       <c r="AX42" s="13"/>
-      <c r="AY42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
@@ -17144,54 +17082,46 @@
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
-      <c r="BI42" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI42" s="23"/>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>5 kg</t>
+          <t>5,49 Kilograms</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>5.00 kg</t>
+          <t>5.49 kg</t>
         </is>
       </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>43 x 19.5 x 34 cm</t>
-        </is>
-      </c>
-      <c r="BM42" s="23" t="inlineStr">
-        <is>
-          <t>43.00 x 19.50 x 34.00 cm</t>
-        </is>
-      </c>
+          <t>43P x 19l x 34H centimètres</t>
+        </is>
+      </c>
+      <c r="BM42" s="23"/>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>5.1 kg</t>
+          <t>5.49 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>5.10 kg</t>
+          <t>5.49 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>43 x 34 x 19.5 cm</t>
+          <t>44.4 x 34.3 x 20.2 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>43.00 x 34.00 x 19.50 cm</t>
+          <t>44.40 x 34.30 x 20.20 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17202,40 +17132,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0GDCZ7BWK</t>
+          <t>B01HZUX61M</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
+          <t>Tech'N'Fast</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/EFD3CB9F-9686-4148-8B39-B39106076EB5?lp_asin=B0GDCZ7BWK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>HYCHIKA Shampouineuse Canapé,Nettoyeur Canapé Tissu 1800Ws17 kPa Injecteur Extracteur Portable,avec Double Réservoir et Aut</t>
+          <t>Nettoyant textile concentré, canapé, moquette, tapis, sièges auto, détachant, dissout les tâches et neutralise les odeurs - B</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GDCZ7BWK?psc=1</t>
+          <t>https://www.amazon.fr/dp/B01HZUX61M?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51aWYbD9oWL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51k6bvKW11L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0GDCZ7BWK</t>
+          <t>B01HZUX61M</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17249,13 +17179,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>31125</v>
+        <v>7857</v>
       </c>
       <c r="P43" s="15">
-        <v>6591</v>
+        <v>698</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17264,83 +17194,101 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>62</v>
+        <v>200</v>
       </c>
       <c r="U43" s="16">
-        <v>0.12</v>
+        <v>1.9</v>
       </c>
       <c r="V43" s="15">
-        <v>6744</v>
-      </c>
-      <c r="W43" s="15"/>
-      <c r="X43" s="15"/>
+        <v>5680</v>
+      </c>
+      <c r="W43" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X43" s="15">
+        <v>3383</v>
+      </c>
       <c r="Y43" s="19">
         <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>90.64</v>
+        <v>28.4</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="19">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="AE43" s="15">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AF43" s="21">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.5806</v>
+        <v>0.025</v>
       </c>
       <c r="AH43" s="20">
-        <v>8.68</v>
+        <v>11.12</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.77</v>
+        <v>0.46</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2017-12-18</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>128</v>
+        <v>3186</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN43" s="13"/>
       <c r="AO43" s="13"/>
       <c r="AP43"/>
       <c r="AQ43" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR43" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>DistriPro</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU43" s="13"/>
-      <c r="AV43" s="14"/>
-      <c r="AW43" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU43" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AV43" s="14" t="inlineStr">
+        <is>
+          <t>Grisy Suisnes 77166 FR</t>
+        </is>
+      </c>
+      <c r="AW43" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA</t>
+        </is>
+      </c>
       <c r="AX43" s="13"/>
       <c r="AY43" s="13"/>
       <c r="AZ43" s="13"/>
@@ -17363,45 +17311,37 @@
       <c r="BI43" s="23"/>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>5,49 Kilograms</t>
+          <t>200 grammes</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>5.49 kg</t>
+          <t>200.00 g</t>
         </is>
       </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>43P x 19l x 34H centimètres</t>
-        </is>
-      </c>
-      <c r="BM43" s="23"/>
+          <t>18 x 14 x 25 cm</t>
+        </is>
+      </c>
+      <c r="BM43" s="23" t="inlineStr">
+        <is>
+          <t>18.00 x 14.00 x 25.00 cm</t>
+        </is>
+      </c>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>5.49 kg</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>5.49 kg</t>
-        </is>
-      </c>
-      <c r="BP43" s="23" t="inlineStr">
-        <is>
-          <t>44.4 x 34.3 x 20.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ43" s="23" t="inlineStr">
-        <is>
-          <t>44.40 x 34.30 x 20.20 cm</t>
-        </is>
-      </c>
-      <c r="BR43" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+          <t>200.00 g</t>
+        </is>
+      </c>
+      <c r="BP43" s="23"/>
+      <c r="BQ43" s="23"/>
+      <c r="BR43" s="13"/>
     </row>
     <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
@@ -17410,40 +17350,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B01HZUX61M</t>
+          <t>B08KXVXC82</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Tech'N'Fast</t>
+          <t>MEDION</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Nettoyant textile concentré, canapé, moquette, tapis, sièges auto, détachant, dissout les tâches et neutralise les odeurs - B</t>
+          <t>MEDION Nettoyeur de tissus injecteur extracteur (Aspirateur eau pour tissus, moquettes et sièges auto, réservoir d'eau propre</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B01HZUX61M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B08KXVXC82?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51k6bvKW11L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41+Q-FdsUUL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B01HZUX61M</t>
+          <t>B08KXVXC82</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17457,13 +17397,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>7857</v>
+        <v>27404</v>
       </c>
       <c r="P44" s="15">
-        <v>698</v>
+        <v>-32952</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.08</v>
+        <v>-1.44</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17472,65 +17412,57 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>200</v>
-      </c>
-      <c r="U44" s="16">
-        <v>1.9</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="U44" s="16"/>
       <c r="V44" s="15">
-        <v>5680</v>
-      </c>
-      <c r="W44" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X44" s="15">
-        <v>3383</v>
-      </c>
+        <v>5621</v>
+      </c>
+      <c r="W44" s="15"/>
+      <c r="X44" s="15"/>
       <c r="Y44" s="19">
         <v>1</v>
       </c>
       <c r="Z44" s="20">
-        <v>28.4</v>
+        <v>74.95</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="19">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="AE44" s="15">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AF44" s="21">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.025</v>
+        <v>0.1867</v>
       </c>
       <c r="AH44" s="20">
-        <v>11.12</v>
+        <v>8.89</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2017-12-18</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>3186</v>
+        <v>136</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
@@ -17540,31 +17472,31 @@
         <v>10</v>
       </c>
       <c r="AR44" s="19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>DistriPro</t>
+          <t>medionshop-deutschland</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU44" s="13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="AV44" s="14" t="inlineStr">
         <is>
-          <t>Grisy Suisnes 77166 FR</t>
+          <t>Essen 45307 DE</t>
         </is>
       </c>
       <c r="AW44" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N</t>
         </is>
       </c>
       <c r="AX44" s="13"/>
@@ -17577,11 +17509,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD44" s="13"/>
       <c r="BE44" s="13"/>
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
@@ -17589,37 +17517,45 @@
       <c r="BI44" s="23"/>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>200 grammes</t>
+          <t>4,5 Kilograms</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>200.00 g</t>
+          <t>4.50 kg</t>
         </is>
       </c>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>18 x 14 x 25 cm</t>
-        </is>
-      </c>
-      <c r="BM44" s="23" t="inlineStr">
-        <is>
-          <t>18.00 x 14.00 x 25.00 cm</t>
-        </is>
-      </c>
+          <t>24P x 31,7l x 35H centimètres</t>
+        </is>
+      </c>
+      <c r="BM44" s="23"/>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>6.05 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>200.00 g</t>
-        </is>
-      </c>
-      <c r="BP44" s="23"/>
-      <c r="BQ44" s="23"/>
-      <c r="BR44" s="13"/>
+          <t>6.05 kg</t>
+        </is>
+      </c>
+      <c r="BP44" s="23" t="inlineStr">
+        <is>
+          <t>37.6 x 37.1 x 26.9 cm</t>
+        </is>
+      </c>
+      <c r="BQ44" s="23" t="inlineStr">
+        <is>
+          <t>37.60 x 37.10 x 26.90 cm</t>
+        </is>
+      </c>
+      <c r="BR44" s="13" t="inlineStr">
+        <is>
+          <t>轻型标准大件</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="13">
@@ -17628,40 +17564,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
+          <t>B0FS2B5W6P</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>MEDION</t>
+          <t>LEHMANN</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>MEDION Nettoyeur de tissus injecteur extracteur (Aspirateur eau pour tissus, moquettes et sièges auto, réservoir d'eau propre</t>
+          <t>LEHMANN EasyWash Shampouineuse Canapé 2 en 1, Nettoyage Puissant pour Taches Résistantes, Doppio Serbatoio, Nettoyeur Canapé,</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B08KXVXC82?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FS2B5W6P?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41+Q-FdsUUL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51ZfyHUDyDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B08KXVXC82</t>
+          <t>B0FS2B5W6P</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17675,13 +17611,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>27404</v>
+        <v>29434</v>
       </c>
       <c r="P45" s="15">
-        <v>-32952</v>
+        <v>1296</v>
       </c>
       <c r="Q45" s="16">
-        <v>-1.44</v>
+        <v>0.05</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17690,15 +17626,17 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>75</v>
-      </c>
-      <c r="U45" s="16"/>
+        <v>77</v>
+      </c>
+      <c r="U45" s="16">
+        <v>2.95</v>
+      </c>
       <c r="V45" s="15">
-        <v>5621</v>
+        <v>5004</v>
       </c>
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
@@ -17706,37 +17644,37 @@
         <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>74.95</v>
+        <v>64.99</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="AE45" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.1867</v>
+        <v>0.2208</v>
       </c>
       <c r="AH45" s="20">
         <v>8.89</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>136</v>
+        <v>290</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
@@ -17750,11 +17688,11 @@
         <v>10</v>
       </c>
       <c r="AR45" s="19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>medionshop-deutschland</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
@@ -17764,21 +17702,25 @@
       </c>
       <c r="AU45" s="13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="AV45" s="14" t="inlineStr">
         <is>
-          <t>Essen 45307 DE</t>
+          <t>Greater Poland 63-100 PL</t>
         </is>
       </c>
       <c r="AW45" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
         </is>
       </c>
       <c r="AX45" s="13"/>
-      <c r="AY45" s="13"/>
+      <c r="AY45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
@@ -17792,7 +17734,11 @@
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
-      <c r="BI45" s="23"/>
+      <c r="BI45" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
           <t>4,5 Kilograms</t>
@@ -17805,28 +17751,28 @@
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>24P x 31,7l x 35H centimètres</t>
+          <t>31,5P x 24l x 35,5H centimètres</t>
         </is>
       </c>
       <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>6.05 kg</t>
+          <t>5.66 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>6.05 kg</t>
+          <t>5.66 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>37.6 x 37.1 x 26.9 cm</t>
+          <t>38 x 36.2 x 26.2 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>37.60 x 37.10 x 26.90 cm</t>
+          <t>38.00 x 36.20 x 26.20 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
@@ -17842,40 +17788,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0FS2B5W6P</t>
+          <t>B0GLNFSYRW</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN</t>
+          <t>Vozascly</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vozascly</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN EasyWash Shampouineuse Canapé 2 en 1, Nettoyage Puissant pour Taches Résistantes, Doppio Serbatoio, Nettoyeur Canapé,</t>
+          <t>Vozascly F1 Aspirateur-Laveur de Tissus pour Canapés, Nettoyeur pour Tapis et Meubles Tissés, 600W+1200W Lave et Sèche en Un,</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FS2B5W6P?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GLNFSYRW?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51ZfyHUDyDL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41zOwfkwiCL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0FS2B5W6P</t>
+          <t>B0GLNFSYRW</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17889,13 +17835,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>29434</v>
+        <v>63075</v>
       </c>
       <c r="P46" s="15">
-        <v>1296</v>
+        <v>37916</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.05</v>
+        <v>0.32</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -17904,17 +17850,15 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>60</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>77</v>
-      </c>
-      <c r="U46" s="16">
-        <v>2.95</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="U46" s="16"/>
       <c r="V46" s="15">
-        <v>5004</v>
+        <v>4000</v>
       </c>
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
@@ -17922,37 +17866,37 @@
         <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>64.99</v>
+        <v>159.99</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="AE46" s="15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="21">
         <v>4.4</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.2208</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="20">
-        <v>8.89</v>
+        <v>8.68</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
@@ -17963,14 +17907,14 @@
       <c r="AO46" s="13"/>
       <c r="AP46"/>
       <c r="AQ46" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR46" s="19">
         <v>2</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>TEONIK IOANNIS SINGLE MEMBER P.C.</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
@@ -17980,25 +17924,21 @@
       </c>
       <c r="AU46" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="AV46" s="14" t="inlineStr">
         <is>
-          <t>Greater Poland 63-100 PL</t>
+          <t>THESSALONIKI 54629 GR</t>
         </is>
       </c>
       <c r="AW46" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AEBC603LGC1S2</t>
         </is>
       </c>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
@@ -18012,45 +17952,41 @@
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>4,5 Kilograms</t>
+          <t>6,71 Kilograms</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>6.71 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>31,5P x 24l x 35,5H centimètres</t>
+          <t>8P x 25l x 18H centimètres</t>
         </is>
       </c>
       <c r="BM46" s="23"/>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>5.66 kg</t>
+          <t>6.71 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>5.66 kg</t>
+          <t>6.71 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>38 x 36.2 x 26.2 cm</t>
+          <t>43.9 x 35.6 x 20.1 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>38.00 x 36.20 x 26.20 cm</t>
+          <t>43.90 x 35.60 x 20.10 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
@@ -18066,40 +18002,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0GLNFSYRW</t>
+          <t>B0FVG6BSSM</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>Vozascly</t>
+          <t>DUSTGO</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vozascly</t>
+          <t>https://www.amazon.fr/stores/DUSTGO/page/5BB8238D-5F39-4CBF-9761-843DEA90854E?lp_asin=B0FVG6BSSM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Vozascly F1 Aspirateur-Laveur de Tissus pour Canapés, Nettoyeur pour Tapis et Meubles Tissés, 600W+1200W Lave et Sèche en Un,</t>
+          <t>DUSTGO - Dustgo Max, Shampouineuse Tapis/Moquettes, Canapé &amp; Matelas – 800W, Double Réservoir 2,6L/1,3L, Brosse Turbo Rotativ</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GLNFSYRW?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FVG6BSSM?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41zOwfkwiCL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31QgM7vrpjL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0GLNFSYRW</t>
+          <t>B0FVG6BSSM</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -18113,13 +18049,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>63075</v>
+        <v>51633</v>
       </c>
       <c r="P47" s="15">
-        <v>37916</v>
+        <v>183292</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.32</v>
+        <v>0.84</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -18128,15 +18064,15 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="U47" s="16"/>
       <c r="V47" s="15">
-        <v>4000</v>
+        <v>3996</v>
       </c>
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
@@ -18144,37 +18080,37 @@
         <v>1</v>
       </c>
       <c r="Z47" s="20">
-        <v>159.99</v>
+        <v>99.9</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="19">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="AE47" s="15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF47" s="21">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AG47" s="22">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH47" s="20">
-        <v>8.68</v>
+        <v>11.24</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>210</v>
+        <v>327</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
@@ -18184,15 +18120,13 @@
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
-      <c r="AQ47" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ47" s="19"/>
       <c r="AR47" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>TEONIK IOANNIS SINGLE MEMBER P.C.</t>
+          <t>DUSTGO FR</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
@@ -18202,17 +18136,17 @@
       </c>
       <c r="AU47" s="13" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="AV47" s="14" t="inlineStr">
         <is>
-          <t>THESSALONIKI 54629 GR</t>
+          <t>Dublin Dublin D22 P3K7 IE</t>
         </is>
       </c>
       <c r="AW47" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AEBC603LGC1S2</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XX0VNO0IQB6L</t>
         </is>
       </c>
       <c r="AX47" s="13"/>
@@ -18225,7 +18159,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD47" s="13"/>
+      <c r="BD47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE47" s="13"/>
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
@@ -18233,38 +18171,38 @@
       <c r="BI47" s="23"/>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>6,71 Kilograms</t>
+          <t>6,8 Kilograms</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>6.71 kg</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>8P x 25l x 18H centimètres</t>
+          <t>36P x 30l x 112H centimètres</t>
         </is>
       </c>
       <c r="BM47" s="23"/>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>6.71 kg</t>
+          <t>6.8 kg</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>6.71 kg</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>43.9 x 35.6 x 20.1 cm</t>
+          <t>61 x 45 x 34 cm</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>43.90 x 35.60 x 20.10 cm</t>
+          <t>61.00 x 45.00 x 34.00 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
@@ -18280,40 +18218,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0FVG6BSSM</t>
+          <t>B0FN7HZHWY</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>DUSTGO</t>
+          <t>Livatro</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/DUSTGO/page/5BB8238D-5F39-4CBF-9761-843DEA90854E?lp_asin=B0FVG6BSSM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>DUSTGO - Dustgo Max, Shampouineuse Tapis/Moquettes, Canapé &amp; Matelas – 800W, Double Réservoir 2,6L/1,3L, Brosse Turbo Rotativ</t>
+          <t>Livatro Nettoyant Tapis et Canapés, Concentré 1:30, Faible Mousse, 500 mlsDilution 1:30, 1 dose de produit pour 30 doses d'</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FVG6BSSM?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FN7HZHWY?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31QgM7vrpjL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/310AHvq-mvL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0FVG6BSSM</t>
+          <t>B0FN7HZHWY</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18327,13 +18265,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>51633</v>
+        <v>40081</v>
       </c>
       <c r="P48" s="15">
-        <v>183292</v>
+        <v>15730</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.84</v>
+        <v>0.2</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18342,15 +18280,17 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>40</v>
-      </c>
-      <c r="U48" s="16"/>
+        <v>34</v>
+      </c>
+      <c r="U48" s="16">
+        <v>-0.92</v>
+      </c>
       <c r="V48" s="15">
-        <v>3996</v>
+        <v>476</v>
       </c>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
@@ -18358,37 +18298,37 @@
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>99.9</v>
+        <v>13.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AE48" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF48" s="21">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.05</v>
+        <v>0.0294</v>
       </c>
       <c r="AH48" s="20">
-        <v>11.24</v>
+        <v>5.98</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
@@ -18398,13 +18338,15 @@
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
-      <c r="AQ48" s="19"/>
+      <c r="AQ48" s="19">
+        <v>10</v>
+      </c>
       <c r="AR48" s="19">
         <v>1</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>DUSTGO FR</t>
+          <t>HOORAY Group</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
@@ -18414,17 +18356,17 @@
       </c>
       <c r="AU48" s="13" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>Dublin Dublin D22 P3K7 IE</t>
+          <t>HK 999077 HK</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XX0VNO0IQB6L</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
@@ -18437,11 +18379,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD48" s="13"/>
       <c r="BE48" s="13"/>
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
@@ -18449,43 +18387,47 @@
       <c r="BI48" s="23"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>6,8 Kilograms</t>
+          <t>600 grammes</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>6.80 kg</t>
+          <t>600.00 g</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>36P x 30l x 112H centimètres</t>
-        </is>
-      </c>
-      <c r="BM48" s="23"/>
+          <t>20 x 9,3 x 6,5 cm</t>
+        </is>
+      </c>
+      <c r="BM48" s="23" t="inlineStr">
+        <is>
+          <t>20.00 x 9.30 x 6.50 cm</t>
+        </is>
+      </c>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>6.8 kg</t>
+          <t>630 g</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>6.80 kg</t>
+          <t>630.00 g</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>61 x 45 x 34 cm</t>
+          <t>20 x 9.3 x 6.5 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>61.00 x 45.00 x 34.00 cm</t>
+          <t>20.00 x 9.30 x 6.50 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -18496,40 +18438,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0FN7HZHWY</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>Livatro</t>
+          <t>Hearten</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Livatro Nettoyant Tapis et Canapés, Concentré 1:30, Faible Mousse, 500 mlsDilution 1:30, 1 dose de produit pour 30 doses d'</t>
+          <t>Hearten Shampouineuse Canapé, Aspiration 22kPa, avec AutonettoyantsNettoyeur Canapé Tissu, Compact et Portable, 1.5L Réserv</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FN7HZHWY?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H263J8GJ?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/310AHvq-mvL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0FN7HZHWY</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -18543,13 +18485,11 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>40081</v>
-      </c>
-      <c r="P49" s="15">
-        <v>15730</v>
-      </c>
+        <v>12293</v>
+      </c>
+      <c r="P49" s="15"/>
       <c r="Q49" s="16">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -18558,17 +18498,15 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>34</v>
-      </c>
-      <c r="U49" s="16">
-        <v>-0.92</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="U49" s="16"/>
       <c r="V49" s="15">
-        <v>476</v>
+        <v>360</v>
       </c>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
@@ -18576,37 +18514,35 @@
         <v>1</v>
       </c>
       <c r="Z49" s="20">
-        <v>13.99</v>
+        <v>89.99</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="2"/>
       <c r="AD49" s="19">
-        <v>25</v>
-      </c>
-      <c r="AE49" s="15">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AE49" s="15"/>
       <c r="AF49" s="21">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.0294</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="20">
-        <v>5.98</v>
+        <v>7.93</v>
       </c>
       <c r="AI49" s="16">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>273</v>
+        <v>15</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
@@ -18617,14 +18553,14 @@
       <c r="AO49" s="13"/>
       <c r="AP49"/>
       <c r="AQ49" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR49" s="19">
         <v>1</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>HOORAY Group</t>
+          <t>Hearten Direct</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
@@ -18639,12 +18575,12 @@
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>HK 999077 HK</t>
+          <t>Hong Kong 999077 HK</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
@@ -18657,7 +18593,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD49" s="13"/>
+      <c r="BD49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
@@ -18665,47 +18605,43 @@
       <c r="BI49" s="23"/>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>600 grammes</t>
+          <t>2,5 Kilograms</t>
         </is>
       </c>
       <c r="BK49" s="23" t="inlineStr">
         <is>
-          <t>600.00 g</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>20 x 9,3 x 6,5 cm</t>
-        </is>
-      </c>
-      <c r="BM49" s="23" t="inlineStr">
-        <is>
-          <t>20.00 x 9.30 x 6.50 cm</t>
-        </is>
-      </c>
+          <t>23,2P x 29,9l x 17,3H centimètres</t>
+        </is>
+      </c>
+      <c r="BM49" s="23"/>
       <c r="BN49" s="23" t="inlineStr">
         <is>
-          <t>630 g</t>
+          <t>2.4 kg</t>
         </is>
       </c>
       <c r="BO49" s="23" t="inlineStr">
         <is>
-          <t>630.00 g</t>
+          <t>2.40 kg</t>
         </is>
       </c>
       <c r="BP49" s="23" t="inlineStr">
         <is>
-          <t>20 x 9.3 x 6.5 cm</t>
+          <t>32 x 31.5 x 19 cm</t>
         </is>
       </c>
       <c r="BQ49" s="23" t="inlineStr">
         <is>
-          <t>20.00 x 9.30 x 6.50 cm</t>
+          <t>32.00 x 31.50 x 19.00 cm</t>
         </is>
       </c>
       <c r="BR49" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -18716,40 +18652,40 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0H263J8GJ</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Hearten</t>
+          <t>Redkey</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Redkey/page/02737A30-44FC-4E51-B18E-EED743710F72?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Hearten Shampouineuse Canapé, Aspiration 22kPa, avec AutonettoyantsNettoyeur Canapé Tissu, Compact et Portable, 1.5L Réserv</t>
+          <t>Redkey Rd-F1 Shampouineuse, 4 en 1 Aspirateur Laveur à Vapeur avec 26000Pa d'Aspiration, 1800W Nettoyage en Profondeur pour T</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H263J8GJ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H4TXR27S?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0H263J8GJ</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -18763,7 +18699,7 @@
         </is>
       </c>
       <c r="O50" s="15">
-        <v>12293</v>
+        <v>25447</v>
       </c>
       <c r="P50" s="15"/>
       <c r="Q50" s="16">
@@ -18776,91 +18712,69 @@
       </c>
       <c r="S50" s="18" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>4</v>
-      </c>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="T50" s="15"/>
       <c r="U50" s="16"/>
-      <c r="V50" s="15">
-        <v>360</v>
-      </c>
+      <c r="V50" s="15"/>
       <c r="W50" s="15"/>
       <c r="X50" s="15"/>
       <c r="Y50" s="19">
         <v>1</v>
       </c>
       <c r="Z50" s="20">
-        <v>89.99</v>
+        <v>139.99</v>
       </c>
       <c r="AA50"/>
       <c r="AB50"/>
       <c r="AC50" s="2"/>
-      <c r="AD50" s="19">
-        <v>2</v>
-      </c>
+      <c r="AD50" s="19"/>
       <c r="AE50" s="15"/>
-      <c r="AF50" s="21">
-        <v>3.6</v>
-      </c>
+      <c r="AF50" s="21"/>
       <c r="AG50" s="22">
         <v>0</v>
       </c>
       <c r="AH50" s="20">
-        <v>7.93</v>
+        <v>9.32</v>
       </c>
       <c r="AI50" s="16">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="AJ50"/>
       <c r="AK50" s="13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AL50" s="19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM50" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN50" s="13"/>
       <c r="AO50" s="13"/>
       <c r="AP50"/>
-      <c r="AQ50" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ50" s="19"/>
       <c r="AR50" s="19">
         <v>1</v>
       </c>
       <c r="AS50" s="14" t="inlineStr">
         <is>
-          <t>Hearten Direct</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT50" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>Hong Kong 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU50" s="13"/>
+      <c r="AV50" s="14"/>
+      <c r="AW50" s="13"/>
       <c r="AX50" s="13"/>
       <c r="AY50" s="13"/>
       <c r="AZ50" s="13"/>
@@ -18871,11 +18785,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD50" s="13"/>
       <c r="BE50" s="13"/>
       <c r="BF50" s="13"/>
       <c r="BG50" s="13"/>
@@ -18883,225 +18793,37 @@
       <c r="BI50" s="23"/>
       <c r="BJ50" s="23" t="inlineStr">
         <is>
-          <t>2,5 Kilograms</t>
+          <t>6,8 Kilograms</t>
         </is>
       </c>
       <c r="BK50" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>23,2P x 29,9l x 17,3H centimètres</t>
-        </is>
-      </c>
+          <t>6.80 kg</t>
+        </is>
+      </c>
+      <c r="BL50" s="23"/>
       <c r="BM50" s="23"/>
       <c r="BN50" s="23" t="inlineStr">
         <is>
-          <t>2.4 kg</t>
+          <t>6.8 kg</t>
         </is>
       </c>
       <c r="BO50" s="23" t="inlineStr">
         <is>
-          <t>2.40 kg</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BP50" s="23" t="inlineStr">
         <is>
-          <t>32 x 31.5 x 19 cm</t>
+          <t>37 x 35 x 35 cm</t>
         </is>
       </c>
       <c r="BQ50" s="23" t="inlineStr">
         <is>
-          <t>32.00 x 31.50 x 19.00 cm</t>
+          <t>37.00 x 35.00 x 35.00 cm</t>
         </is>
       </c>
       <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0H4TXR27S</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Redkey</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/stores/Redkey/page/02737A30-44FC-4E51-B18E-EED743710F72?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Redkey Rd-F1 Shampouineuse, 4 en 1 Aspirateur Laveur à Vapeur avec 26000Pa d'Aspiration, 1800W Nettoyage en Profondeur pour T</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0H4TXR27S?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0H4TXR27S</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>25447</v>
-      </c>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16">
-        <v>0</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>139.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19"/>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21"/>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>9.32</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.79</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>16</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>6,8 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>6.80 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>6.8 kg</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>6.80 kg</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>37 x 35 x 35 cm</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>37.00 x 35.00 x 35.00 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>轻型标准大件</t>
         </is>
@@ -19323,172 +19045,165 @@
     <hyperlink ref="L30" r:id="rId210" tooltip="https://www.amazon.fr/dp/B0FL7JJGMG"/>
     <hyperlink ref="M30" r:id="rId211" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N30" r:id="rId212"/>
-    <hyperlink ref="C31" r:id="rId213" tooltip="https://www.amazon.fr/dp/B07999DC2C"/>
-    <hyperlink ref="G31" r:id="rId214" tooltip="https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B07999DC2C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId215" tooltip="https://www.amazon.fr/dp/B07999DC2C?psc=1"/>
-    <hyperlink ref="K31" r:id="rId216" tooltip="https://images-na.ssl-images-amazon.com/images/I/61aI3+gXJwL._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId217" tooltip="https://www.amazon.fr/dp/B07999DC2C"/>
+    <hyperlink ref="C31" r:id="rId213" tooltip="https://www.amazon.fr/dp/B0FD9R33PF"/>
+    <hyperlink ref="G31" r:id="rId214" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=welsauber"/>
+    <hyperlink ref="J31" r:id="rId215" tooltip="https://www.amazon.fr/dp/B0FD9R33PF?psc=1"/>
+    <hyperlink ref="K31" r:id="rId216" tooltip="https://images-na.ssl-images-amazon.com/images/I/715cAyIFD7L._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId217" tooltip="https://www.amazon.fr/dp/B0FD9R33PF"/>
     <hyperlink ref="M31" r:id="rId218" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N31" r:id="rId219"/>
-    <hyperlink ref="C32" r:id="rId220" tooltip="https://www.amazon.fr/dp/B0FD9R33PF"/>
-    <hyperlink ref="G32" r:id="rId221" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=welsauber"/>
-    <hyperlink ref="J32" r:id="rId222" tooltip="https://www.amazon.fr/dp/B0FD9R33PF?psc=1"/>
-    <hyperlink ref="K32" r:id="rId223" tooltip="https://images-na.ssl-images-amazon.com/images/I/715cAyIFD7L._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId224" tooltip="https://www.amazon.fr/dp/B0FD9R33PF"/>
-    <hyperlink ref="M32" r:id="rId225" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N32" r:id="rId226"/>
-    <hyperlink ref="AW32" r:id="rId227" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYFJ11UI07NEJ"/>
-    <hyperlink ref="C33" r:id="rId228" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
-    <hyperlink ref="G33" r:id="rId229" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J33" r:id="rId230" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1"/>
-    <hyperlink ref="K33" r:id="rId231" tooltip="https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId232" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
-    <hyperlink ref="M33" r:id="rId233" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N33" r:id="rId234"/>
-    <hyperlink ref="AW33" r:id="rId235" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C34" r:id="rId236" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV"/>
-    <hyperlink ref="G34" r:id="rId237" tooltip="https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQWRZLV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J34" r:id="rId238" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV?psc=1"/>
-    <hyperlink ref="K34" r:id="rId239" tooltip="https://images-na.ssl-images-amazon.com/images/I/71LN+xCoF4L._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId240" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV"/>
-    <hyperlink ref="M34" r:id="rId241" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N34" r:id="rId242"/>
-    <hyperlink ref="AW34" r:id="rId243" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A"/>
-    <hyperlink ref="C35" r:id="rId244" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT"/>
-    <hyperlink ref="G35" r:id="rId245" tooltip="https://www.amazon.fr/stores/Vacmaster/page/1389DFA9-3AE6-4105-88E0-C76D00DC1B2D?lp_asin=B0GFKK2WXT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J35" r:id="rId246" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT?psc=1"/>
-    <hyperlink ref="K35" r:id="rId247" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/412kfxWeU6L._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId248" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT"/>
-    <hyperlink ref="M35" r:id="rId249" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N35" r:id="rId250"/>
-    <hyperlink ref="AW35" r:id="rId251" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUAKXO7WRPF4V"/>
-    <hyperlink ref="C36" r:id="rId252" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
-    <hyperlink ref="G36" r:id="rId253" tooltip="https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN"/>
-    <hyperlink ref="J36" r:id="rId254" tooltip="https://www.amazon.fr/dp/B0C3VKT151?psc=1"/>
-    <hyperlink ref="K36" r:id="rId255" tooltip="https://m.media-amazon.com/images/I/41xcF1ROXCL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId256" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
-    <hyperlink ref="M36" r:id="rId257" tooltip="https://www.amazon.fr/b?node=3575161031"/>
-    <hyperlink ref="N36" r:id="rId258"/>
-    <hyperlink ref="AW36" r:id="rId259" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F"/>
-    <hyperlink ref="C37" r:id="rId260" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
-    <hyperlink ref="G37" r:id="rId261" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J37" r:id="rId262" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
-    <hyperlink ref="K37" r:id="rId263" tooltip="https://images-na.ssl-images-amazon.com/images/I/71nARwekliL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId264" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
-    <hyperlink ref="M37" r:id="rId265" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N37" r:id="rId266"/>
-    <hyperlink ref="AW37" r:id="rId267" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B"/>
-    <hyperlink ref="C38" r:id="rId268" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
-    <hyperlink ref="G38" r:id="rId269" tooltip="https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQBM3W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J38" r:id="rId270" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1?psc=1"/>
-    <hyperlink ref="K38" r:id="rId271" tooltip="https://m.media-amazon.com/images/I/41d4NPDnU9L._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId272" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
-    <hyperlink ref="M38" r:id="rId273" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N38" r:id="rId274"/>
-    <hyperlink ref="AW38" r:id="rId275" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A"/>
-    <hyperlink ref="C39" r:id="rId276" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
-    <hyperlink ref="G39" r:id="rId277" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId278" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
-    <hyperlink ref="K39" r:id="rId279" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41mvaF7mrKL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId280" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="AW31" r:id="rId220" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYFJ11UI07NEJ"/>
+    <hyperlink ref="C32" r:id="rId221" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
+    <hyperlink ref="G32" r:id="rId222" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J32" r:id="rId223" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1"/>
+    <hyperlink ref="K32" r:id="rId224" tooltip="https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId225" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
+    <hyperlink ref="M32" r:id="rId226" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N32" r:id="rId227"/>
+    <hyperlink ref="AW32" r:id="rId228" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C33" r:id="rId229" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV"/>
+    <hyperlink ref="G33" r:id="rId230" tooltip="https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQWRZLV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J33" r:id="rId231" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV?psc=1"/>
+    <hyperlink ref="K33" r:id="rId232" tooltip="https://images-na.ssl-images-amazon.com/images/I/71LN+xCoF4L._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId233" tooltip="https://www.amazon.fr/dp/B0GHQWRZLV"/>
+    <hyperlink ref="M33" r:id="rId234" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N33" r:id="rId235"/>
+    <hyperlink ref="AW33" r:id="rId236" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A"/>
+    <hyperlink ref="C34" r:id="rId237" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT"/>
+    <hyperlink ref="G34" r:id="rId238" tooltip="https://www.amazon.fr/stores/Vacmaster/page/1389DFA9-3AE6-4105-88E0-C76D00DC1B2D?lp_asin=B0GFKK2WXT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J34" r:id="rId239" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT?psc=1"/>
+    <hyperlink ref="K34" r:id="rId240" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/412kfxWeU6L._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId241" tooltip="https://www.amazon.fr/dp/B0GFKK2WXT"/>
+    <hyperlink ref="M34" r:id="rId242" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N34" r:id="rId243"/>
+    <hyperlink ref="AW34" r:id="rId244" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUAKXO7WRPF4V"/>
+    <hyperlink ref="C35" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
+    <hyperlink ref="G35" r:id="rId246" tooltip="https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN"/>
+    <hyperlink ref="J35" r:id="rId247" tooltip="https://www.amazon.fr/dp/B0C3VKT151?psc=1"/>
+    <hyperlink ref="K35" r:id="rId248" tooltip="https://m.media-amazon.com/images/I/41xcF1ROXCL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId249" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
+    <hyperlink ref="M35" r:id="rId250" tooltip="https://www.amazon.fr/b?node=3575161031"/>
+    <hyperlink ref="N35" r:id="rId251"/>
+    <hyperlink ref="AW35" r:id="rId252" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F"/>
+    <hyperlink ref="C36" r:id="rId253" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
+    <hyperlink ref="G36" r:id="rId254" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J36" r:id="rId255" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
+    <hyperlink ref="K36" r:id="rId256" tooltip="https://images-na.ssl-images-amazon.com/images/I/71nARwekliL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId257" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
+    <hyperlink ref="M36" r:id="rId258" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N36" r:id="rId259"/>
+    <hyperlink ref="AW36" r:id="rId260" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B"/>
+    <hyperlink ref="C37" r:id="rId261" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
+    <hyperlink ref="G37" r:id="rId262" tooltip="https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GHQBM3W1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J37" r:id="rId263" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1?psc=1"/>
+    <hyperlink ref="K37" r:id="rId264" tooltip="https://m.media-amazon.com/images/I/41d4NPDnU9L._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId265" tooltip="https://www.amazon.fr/dp/B0GHQBM3W1"/>
+    <hyperlink ref="M37" r:id="rId266" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N37" r:id="rId267"/>
+    <hyperlink ref="AW37" r:id="rId268" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A"/>
+    <hyperlink ref="C38" r:id="rId269" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="G38" r:id="rId270" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId271" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
+    <hyperlink ref="K38" r:id="rId272" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41mvaF7mrKL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId273" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="M38" r:id="rId274" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N38" r:id="rId275"/>
+    <hyperlink ref="C39" r:id="rId276" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4"/>
+    <hyperlink ref="G39" r:id="rId277" tooltip="https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GZVZYBP4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J39" r:id="rId278" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4?psc=1"/>
+    <hyperlink ref="K39" r:id="rId279" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41IR-fMqT2L._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId280" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4"/>
     <hyperlink ref="M39" r:id="rId281" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N39" r:id="rId282"/>
-    <hyperlink ref="C40" r:id="rId283" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4"/>
-    <hyperlink ref="G40" r:id="rId284" tooltip="https://www.amazon.fr/stores/SIMPLUS/page/D9B53708-AF6E-42C6-BF70-C3FD10A87491?lp_asin=B0GZVZYBP4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J40" r:id="rId285" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4?psc=1"/>
-    <hyperlink ref="K40" r:id="rId286" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41IR-fMqT2L._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId287" tooltip="https://www.amazon.fr/dp/B0GZVZYBP4"/>
-    <hyperlink ref="M40" r:id="rId288" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N40" r:id="rId289"/>
-    <hyperlink ref="AW40" r:id="rId290" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A"/>
-    <hyperlink ref="C41" r:id="rId291" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="G41" r:id="rId292" tooltip="https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J41" r:id="rId293" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1"/>
-    <hyperlink ref="K41" r:id="rId294" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41EDgJP8-JL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId295" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="M41" r:id="rId296" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N41" r:id="rId297"/>
-    <hyperlink ref="AW41" r:id="rId298" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
-    <hyperlink ref="C42" r:id="rId299" tooltip="https://www.amazon.fr/dp/B0H2VRP6P5"/>
-    <hyperlink ref="G42" r:id="rId300" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=STARRYBOT"/>
-    <hyperlink ref="J42" r:id="rId301" tooltip="https://www.amazon.fr/dp/B0H2VRP6P5?psc=1"/>
-    <hyperlink ref="K42" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gQgb5LadL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId303" tooltip="https://www.amazon.fr/dp/B0H2VRP6P5"/>
-    <hyperlink ref="M42" r:id="rId304" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N42" r:id="rId305"/>
-    <hyperlink ref="AW42" r:id="rId306" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ"/>
-    <hyperlink ref="C43" r:id="rId307" tooltip="https://www.amazon.fr/dp/B0GDCZ7BWK"/>
-    <hyperlink ref="G43" r:id="rId308" tooltip="https://www.amazon.fr/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/EFD3CB9F-9686-4148-8B39-B39106076EB5?lp_asin=B0GDCZ7BWK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J43" r:id="rId309" tooltip="https://www.amazon.fr/dp/B0GDCZ7BWK?psc=1"/>
-    <hyperlink ref="K43" r:id="rId310" tooltip="https://m.media-amazon.com/images/I/51aWYbD9oWL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId311" tooltip="https://www.amazon.fr/dp/B0GDCZ7BWK"/>
+    <hyperlink ref="AW39" r:id="rId283" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XKT4QASR154A"/>
+    <hyperlink ref="C40" r:id="rId284" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="G40" r:id="rId285" tooltip="https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J40" r:id="rId286" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1"/>
+    <hyperlink ref="K40" r:id="rId287" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41EDgJP8-JL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId288" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="M40" r:id="rId289" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N40" r:id="rId290"/>
+    <hyperlink ref="AW40" r:id="rId291" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
+    <hyperlink ref="C41" r:id="rId292" tooltip="https://www.amazon.fr/dp/B0H2VRP6P5"/>
+    <hyperlink ref="G41" r:id="rId293" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=STARRYBOT"/>
+    <hyperlink ref="J41" r:id="rId294" tooltip="https://www.amazon.fr/dp/B0H2VRP6P5?psc=1"/>
+    <hyperlink ref="K41" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gQgb5LadL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId296" tooltip="https://www.amazon.fr/dp/B0H2VRP6P5"/>
+    <hyperlink ref="M41" r:id="rId297" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N41" r:id="rId298"/>
+    <hyperlink ref="AW41" r:id="rId299" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ"/>
+    <hyperlink ref="C42" r:id="rId300" tooltip="https://www.amazon.fr/dp/B0GDCZ7BWK"/>
+    <hyperlink ref="G42" r:id="rId301" tooltip="https://www.amazon.fr/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/EFD3CB9F-9686-4148-8B39-B39106076EB5?lp_asin=B0GDCZ7BWK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J42" r:id="rId302" tooltip="https://www.amazon.fr/dp/B0GDCZ7BWK?psc=1"/>
+    <hyperlink ref="K42" r:id="rId303" tooltip="https://m.media-amazon.com/images/I/51aWYbD9oWL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId304" tooltip="https://www.amazon.fr/dp/B0GDCZ7BWK"/>
+    <hyperlink ref="M42" r:id="rId305" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N42" r:id="rId306"/>
+    <hyperlink ref="C43" r:id="rId307" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
+    <hyperlink ref="G43" r:id="rId308" tooltip="https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J43" r:id="rId309" tooltip="https://www.amazon.fr/dp/B01HZUX61M?psc=1"/>
+    <hyperlink ref="K43" r:id="rId310" tooltip="https://images-na.ssl-images-amazon.com/images/I/51k6bvKW11L._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId311" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
     <hyperlink ref="M43" r:id="rId312" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N43" r:id="rId313"/>
-    <hyperlink ref="C44" r:id="rId314" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
-    <hyperlink ref="G44" r:id="rId315" tooltip="https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId316" tooltip="https://www.amazon.fr/dp/B01HZUX61M?psc=1"/>
-    <hyperlink ref="K44" r:id="rId317" tooltip="https://images-na.ssl-images-amazon.com/images/I/51k6bvKW11L._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId318" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
-    <hyperlink ref="M44" r:id="rId319" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N44" r:id="rId320"/>
-    <hyperlink ref="AW44" r:id="rId321" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA"/>
-    <hyperlink ref="C45" r:id="rId322" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
-    <hyperlink ref="G45" r:id="rId323" tooltip="https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J45" r:id="rId324" tooltip="https://www.amazon.fr/dp/B08KXVXC82?psc=1"/>
-    <hyperlink ref="K45" r:id="rId325" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41+Q-FdsUUL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId326" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
-    <hyperlink ref="M45" r:id="rId327" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N45" r:id="rId328"/>
-    <hyperlink ref="AW45" r:id="rId329" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N"/>
-    <hyperlink ref="C46" r:id="rId330" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
-    <hyperlink ref="G46" r:id="rId331" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J46" r:id="rId332" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P?psc=1"/>
-    <hyperlink ref="K46" r:id="rId333" tooltip="https://m.media-amazon.com/images/I/51ZfyHUDyDL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId334" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
-    <hyperlink ref="M46" r:id="rId335" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N46" r:id="rId336"/>
-    <hyperlink ref="AW46" r:id="rId337" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C47" r:id="rId338" tooltip="https://www.amazon.fr/dp/B0GLNFSYRW"/>
-    <hyperlink ref="G47" r:id="rId339" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vozascly"/>
-    <hyperlink ref="J47" r:id="rId340" tooltip="https://www.amazon.fr/dp/B0GLNFSYRW?psc=1"/>
-    <hyperlink ref="K47" r:id="rId341" tooltip="https://m.media-amazon.com/images/I/41zOwfkwiCL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId342" tooltip="https://www.amazon.fr/dp/B0GLNFSYRW"/>
-    <hyperlink ref="M47" r:id="rId343" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N47" r:id="rId344"/>
-    <hyperlink ref="AW47" r:id="rId345" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AEBC603LGC1S2"/>
-    <hyperlink ref="C48" r:id="rId346" tooltip="https://www.amazon.fr/dp/B0FVG6BSSM"/>
-    <hyperlink ref="G48" r:id="rId347" tooltip="https://www.amazon.fr/stores/DUSTGO/page/5BB8238D-5F39-4CBF-9761-843DEA90854E?lp_asin=B0FVG6BSSM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J48" r:id="rId348" tooltip="https://www.amazon.fr/dp/B0FVG6BSSM?psc=1"/>
-    <hyperlink ref="K48" r:id="rId349" tooltip="https://m.media-amazon.com/images/I/31QgM7vrpjL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId350" tooltip="https://www.amazon.fr/dp/B0FVG6BSSM"/>
-    <hyperlink ref="M48" r:id="rId351" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N48" r:id="rId352"/>
-    <hyperlink ref="AW48" r:id="rId353" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XX0VNO0IQB6L"/>
-    <hyperlink ref="C49" r:id="rId354" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY"/>
-    <hyperlink ref="G49" r:id="rId355" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J49" r:id="rId356" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY?psc=1"/>
-    <hyperlink ref="K49" r:id="rId357" tooltip="https://m.media-amazon.com/images/I/310AHvq-mvL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId358" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY"/>
-    <hyperlink ref="M49" r:id="rId359" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N49" r:id="rId360"/>
-    <hyperlink ref="AW49" r:id="rId361" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS"/>
-    <hyperlink ref="C50" r:id="rId362" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
-    <hyperlink ref="G50" r:id="rId363" tooltip="https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId364" tooltip="https://www.amazon.fr/dp/B0H263J8GJ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId365" tooltip="https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId366" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
-    <hyperlink ref="M50" r:id="rId367" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N50" r:id="rId368"/>
-    <hyperlink ref="AW50" r:id="rId369" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
-    <hyperlink ref="C51" r:id="rId370" tooltip="https://www.amazon.fr/dp/B0H4TXR27S"/>
-    <hyperlink ref="G51" r:id="rId371" tooltip="https://www.amazon.fr/stores/Redkey/page/02737A30-44FC-4E51-B18E-EED743710F72?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J51" r:id="rId372" tooltip="https://www.amazon.fr/dp/B0H4TXR27S?psc=1"/>
-    <hyperlink ref="K51" r:id="rId373" tooltip="https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId374" tooltip="https://www.amazon.fr/dp/B0H4TXR27S"/>
-    <hyperlink ref="M51" r:id="rId375" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N51" r:id="rId376"/>
+    <hyperlink ref="AW43" r:id="rId314" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA"/>
+    <hyperlink ref="C44" r:id="rId315" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
+    <hyperlink ref="G44" r:id="rId316" tooltip="https://www.amazon.fr/stores/MEDION/page/6EC95B48-D171-48BD-98A0-9ACD9CF4EA04?lp_asin=B08KXVXC82&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J44" r:id="rId317" tooltip="https://www.amazon.fr/dp/B08KXVXC82?psc=1"/>
+    <hyperlink ref="K44" r:id="rId318" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/41+Q-FdsUUL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId319" tooltip="https://www.amazon.fr/dp/B08KXVXC82"/>
+    <hyperlink ref="M44" r:id="rId320" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N44" r:id="rId321"/>
+    <hyperlink ref="AW44" r:id="rId322" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3191A9OLGYR1N"/>
+    <hyperlink ref="C45" r:id="rId323" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
+    <hyperlink ref="G45" r:id="rId324" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J45" r:id="rId325" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P?psc=1"/>
+    <hyperlink ref="K45" r:id="rId326" tooltip="https://m.media-amazon.com/images/I/51ZfyHUDyDL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId327" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
+    <hyperlink ref="M45" r:id="rId328" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N45" r:id="rId329"/>
+    <hyperlink ref="AW45" r:id="rId330" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C46" r:id="rId331" tooltip="https://www.amazon.fr/dp/B0GLNFSYRW"/>
+    <hyperlink ref="G46" r:id="rId332" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vozascly"/>
+    <hyperlink ref="J46" r:id="rId333" tooltip="https://www.amazon.fr/dp/B0GLNFSYRW?psc=1"/>
+    <hyperlink ref="K46" r:id="rId334" tooltip="https://m.media-amazon.com/images/I/41zOwfkwiCL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId335" tooltip="https://www.amazon.fr/dp/B0GLNFSYRW"/>
+    <hyperlink ref="M46" r:id="rId336" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N46" r:id="rId337"/>
+    <hyperlink ref="AW46" r:id="rId338" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AEBC603LGC1S2"/>
+    <hyperlink ref="C47" r:id="rId339" tooltip="https://www.amazon.fr/dp/B0FVG6BSSM"/>
+    <hyperlink ref="G47" r:id="rId340" tooltip="https://www.amazon.fr/stores/DUSTGO/page/5BB8238D-5F39-4CBF-9761-843DEA90854E?lp_asin=B0FVG6BSSM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J47" r:id="rId341" tooltip="https://www.amazon.fr/dp/B0FVG6BSSM?psc=1"/>
+    <hyperlink ref="K47" r:id="rId342" tooltip="https://m.media-amazon.com/images/I/31QgM7vrpjL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId343" tooltip="https://www.amazon.fr/dp/B0FVG6BSSM"/>
+    <hyperlink ref="M47" r:id="rId344" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N47" r:id="rId345"/>
+    <hyperlink ref="AW47" r:id="rId346" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XX0VNO0IQB6L"/>
+    <hyperlink ref="C48" r:id="rId347" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY"/>
+    <hyperlink ref="G48" r:id="rId348" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId349" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY?psc=1"/>
+    <hyperlink ref="K48" r:id="rId350" tooltip="https://m.media-amazon.com/images/I/310AHvq-mvL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId351" tooltip="https://www.amazon.fr/dp/B0FN7HZHWY"/>
+    <hyperlink ref="M48" r:id="rId352" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N48" r:id="rId353"/>
+    <hyperlink ref="AW48" r:id="rId354" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS"/>
+    <hyperlink ref="C49" r:id="rId355" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
+    <hyperlink ref="G49" r:id="rId356" tooltip="https://www.amazon.fr/stores/ACCUEIL/page/1563F9C6-0006-4650-9087-F76ECFA0D4DE?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J49" r:id="rId357" tooltip="https://www.amazon.fr/dp/B0H263J8GJ?psc=1"/>
+    <hyperlink ref="K49" r:id="rId358" tooltip="https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId359" tooltip="https://www.amazon.fr/dp/B0H263J8GJ"/>
+    <hyperlink ref="M49" r:id="rId360" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N49" r:id="rId361"/>
+    <hyperlink ref="AW49" r:id="rId362" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
+    <hyperlink ref="C50" r:id="rId363" tooltip="https://www.amazon.fr/dp/B0H4TXR27S"/>
+    <hyperlink ref="G50" r:id="rId364" tooltip="https://www.amazon.fr/stores/Redkey/page/02737A30-44FC-4E51-B18E-EED743710F72?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J50" r:id="rId365" tooltip="https://www.amazon.fr/dp/B0H4TXR27S?psc=1"/>
+    <hyperlink ref="K50" r:id="rId366" tooltip="https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg"/>
+    <hyperlink ref="L50" r:id="rId367" tooltip="https://www.amazon.fr/dp/B0H4TXR27S"/>
+    <hyperlink ref="M50" r:id="rId368" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N50" r:id="rId369"/>
   </hyperlinks>
-  <drawing r:id="rId377"/>
+  <drawing r:id="rId370"/>
 </worksheet>
 </file>
 
@@ -19547,18 +19262,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>20727</v>
+        <v>20237</v>
       </c>
       <c r="C2" s="15">
-        <v>1536609</v>
+        <v>1524364</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>74.13562020552902</v>
+        <v>75.32559173790581</v>
       </c>
       <c r="G2" s="22">
-        <v>0.676071498466958</v>
+        <v>0.6708101299390082</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19579,7 +19294,7 @@
         <v>148.26516464471405</v>
       </c>
       <c r="G3" s="22">
-        <v>0.07528214495400874</v>
+        <v>0.07650490586051445</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19600,7 +19315,7 @@
         <v>155.75385745775165</v>
       </c>
       <c r="G4" s="22">
-        <v>0.04439298062495923</v>
+        <v>0.04511402810925484</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19621,7 +19336,7 @@
         <v>102.93918331885317</v>
       </c>
       <c r="G5" s="22">
-        <v>0.03754321873572966</v>
+        <v>0.03815300981172103</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19642,7 +19357,7 @@
         <v>176.7635782747604</v>
       </c>
       <c r="G6" s="22">
-        <v>0.020418814012655752</v>
+        <v>0.0207504640678865</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19663,7 +19378,7 @@
         <v>56.68989819890368</v>
       </c>
       <c r="G7" s="22">
-        <v>0.0416530758692674</v>
+        <v>0.042329620790241315</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19684,7 +19399,7 @@
         <v>99.9006309148265</v>
       </c>
       <c r="G8" s="22">
-        <v>0.020679757322721638</v>
+        <v>0.021015645717316362</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19705,7 +19420,7 @@
         <v>103.13978494623656</v>
       </c>
       <c r="G9" s="22">
-        <v>0.01516732989757975</v>
+        <v>0.015413683373110582</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19726,7 +19441,7 @@
         <v>179.98809523809524</v>
       </c>
       <c r="G10" s="22">
-        <v>0.005479809511383652</v>
+        <v>0.005568814638027049</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19747,7 +19462,7 @@
         <v>97.35315985130111</v>
       </c>
       <c r="G11" s="22">
-        <v>0.00877421880096549</v>
+        <v>0.008916732962079024</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19768,7 +19483,7 @@
         <v>99.28220858895706</v>
       </c>
       <c r="G12" s="22">
-        <v>0.005316719942592472</v>
+        <v>0.005403076107133386</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19789,7 +19504,7 @@
         <v>60.69827586206897</v>
       </c>
       <c r="G13" s="22">
-        <v>0.007567355991910757</v>
+        <v>0.0076902678334659245</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19810,7 +19525,7 @@
         <v>75.99324324324324</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0048274512362189315</v>
+        <v>0.0049058605144524</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19831,7 +19546,7 @@
         <v>28.639769452449567</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0113184160741079</v>
+        <v>0.011502254044020154</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19852,7 +19567,7 @@
         <v>62.64556962025316</v>
       </c>
       <c r="G16" s="22">
-        <v>0.005153630373801291</v>
+        <v>0.005237337576239724</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19873,7 +19588,7 @@
         <v>79.98969072164948</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0031639376345488942</v>
+        <v>0.0032153274993370457</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19894,7 +19609,7 @@
         <v>69.89719626168224</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0034901167721312545</v>
+        <v>0.0035468045611243702</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19915,7 +19630,7 @@
         <v>129.9814814814815</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0017613673429447453</v>
+        <v>0.0017899761336515514</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19936,7 +19651,7 @@
         <v>108.7741935483871</v>
       </c>
       <c r="G20" s="22">
-        <v>0.0020223106530106332</v>
+        <v>0.0020551577830814106</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19957,7 +19672,7 @@
         <v>28.4</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0065235827516472045</v>
+        <v>0.006629541235746487</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19978,7 +19693,7 @@
         <v>74.94666666666667</v>
       </c>
       <c r="G22" s="22">
-        <v>0.002446343531867702</v>
+        <v>0.0024860779634049324</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19999,7 +19714,7 @@
         <v>160.0</v>
       </c>
       <c r="G23" s="22">
-        <v>0.0008154478439559006</v>
+        <v>0.0008286926544683108</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20020,7 +19735,7 @@
         <v>90.0</v>
       </c>
       <c r="G24" s="22">
-        <v>0.0001304716550329441</v>
+        <v>0.00013259082471492973</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20103,18 +19818,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>25965</v>
+        <v>25475</v>
       </c>
       <c r="C2" s="15">
-        <v>2226106</v>
+        <v>2213861</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>85.73487386866937</v>
+        <v>86.9032777232581</v>
       </c>
       <c r="G2" s="22">
-        <v>0.8469241307325983</v>
+        <v>0.8444378149032087</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20135,7 +19850,7 @@
         <v>155.4843492586491</v>
       </c>
       <c r="G3" s="22">
-        <v>0.03959814730249853</v>
+        <v>0.04024131530098117</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20156,7 +19871,7 @@
         <v>56.68989819890368</v>
       </c>
       <c r="G4" s="22">
-        <v>0.0416530758692674</v>
+        <v>0.042329620790241315</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20177,7 +19892,7 @@
         <v>103.13978494623656</v>
       </c>
       <c r="G5" s="22">
-        <v>0.01516732989757975</v>
+        <v>0.015413683373110582</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20198,7 +19913,7 @@
         <v>97.35315985130111</v>
       </c>
       <c r="G6" s="22">
-        <v>0.00877421880096549</v>
+        <v>0.008916732962079024</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20219,7 +19934,7 @@
         <v>157.9795918367347</v>
       </c>
       <c r="G7" s="22">
-        <v>0.004794833322460695</v>
+        <v>0.004872712808273667</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20240,7 +19955,7 @@
         <v>99.28220858895706</v>
       </c>
       <c r="G8" s="22">
-        <v>0.005316719942592472</v>
+        <v>0.005403076107133386</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20261,7 +19976,7 @@
         <v>75.99324324324324</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0048274512362189315</v>
+        <v>0.0049058605144524</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20282,7 +19997,7 @@
         <v>28.639769452449567</v>
       </c>
       <c r="G10" s="22">
-        <v>0.0113184160741079</v>
+        <v>0.011502254044020154</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20303,7 +20018,7 @@
         <v>75.98387096774194</v>
       </c>
       <c r="G11" s="22">
-        <v>0.0040446213060212665</v>
+        <v>0.004110315566162821</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20324,7 +20039,7 @@
         <v>69.89719626168224</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0034901167721312545</v>
+        <v>0.0035468045611243702</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20345,7 +20060,7 @@
         <v>129.9814814814815</v>
       </c>
       <c r="G13" s="22">
-        <v>0.0017613673429447453</v>
+        <v>0.0017899761336515514</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20366,7 +20081,7 @@
         <v>28.4</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0065235827516472045</v>
+        <v>0.006629541235746487</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20387,7 +20102,7 @@
         <v>74.94666666666667</v>
       </c>
       <c r="G15" s="22">
-        <v>0.002446343531867702</v>
+        <v>0.0024860779634049324</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20408,7 +20123,7 @@
         <v>160.0</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0008154478439559006</v>
+        <v>0.0008286926544683108</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20429,7 +20144,7 @@
         <v>99.9</v>
       </c>
       <c r="G17" s="22">
-        <v>0.001304716550329441</v>
+        <v>0.0013259082471492973</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20450,7 +20165,7 @@
         <v>14.0</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0011090090677800249</v>
+        <v>0.0011270220100769027</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20471,7 +20186,7 @@
         <v>90.0</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0001304716550329441</v>
+        <v>0.00013259082471492973</v>
       </c>
     </row>
   </sheetData>
